--- a/medical_surveys_questionnaires/009_cardiology_roi_assessment--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/009_cardiology_roi_assessment--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -908,8 +908,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -937,12 +937,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'significant_gain_(&gt;20%)',_'value':_'significant'}</t>
+          <t>significant_gain_(&gt;20%)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Significant Gain (&gt;20%)', 'value': 'significant'}</t>
+          <t>Significant Gain (&gt;20%)</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'moderate_gain_(10-20%)',_'value':_'moderate'}</t>
+          <t>moderate_gain_(10-20%)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate Gain (10-20%)', 'value': 'moderate'}</t>
+          <t>Moderate Gain (10-20%)</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'slight_gain_(0-10%)',_'value':_'slight'}</t>
+          <t>slight_gain_(0-10%)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Slight Gain (0-10%)', 'value': 'slight'}</t>
+          <t>Slight Gain (0-10%)</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'no_change',_'value':_'none'}</t>
+          <t>no_change</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'No Change', 'value': 'none'}</t>
+          <t>No Change</t>
         </is>
       </c>
     </row>
